--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B165AF66-3C2F-B847-A13A-E220D1AF7849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C00564-7E6B-BC46-A650-A0BA1FEC7211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>NOM</t>
   </si>
@@ -770,7 +770,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7"/>
+      <c r="A1" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C00564-7E6B-BC46-A650-A0BA1FEC7211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372AF762-1E6D-6C47-A866-2CC8E3395F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
   <si>
     <t>NOM</t>
   </si>
@@ -59,18 +59,6 @@
     <t>DELAI MAX</t>
   </si>
   <si>
-    <t>ETAPE 1</t>
-  </si>
-  <si>
-    <t>ETAPE 2</t>
-  </si>
-  <si>
-    <t>ETAPE3</t>
-  </si>
-  <si>
-    <t>ETAPE 4</t>
-  </si>
-  <si>
     <t>2EME PAIEMENT</t>
   </si>
   <si>
@@ -161,9 +149,6 @@
     <t>user06</t>
   </si>
   <si>
-    <t>user07</t>
-  </si>
-  <si>
     <t>user08</t>
   </si>
   <si>
@@ -240,13 +225,49 @@
   </si>
   <si>
     <t>OUI</t>
+  </si>
+  <si>
+    <t>master</t>
+  </si>
+  <si>
+    <t>ARESFRANKLIN</t>
+  </si>
+  <si>
+    <t>FRANKLIN</t>
+  </si>
+  <si>
+    <t>ISSA</t>
+  </si>
+  <si>
+    <t>IssaFATOH</t>
+  </si>
+  <si>
+    <t>FATOH</t>
+  </si>
+  <si>
+    <t>NON</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>DOSSIER COMPLET</t>
+  </si>
+  <si>
+    <t>ETUDE DOSSIER</t>
+  </si>
+  <si>
+    <t>VALIDATION DOSSIER</t>
+  </si>
+  <si>
+    <t>PRODUCTION DOCUMENT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +282,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="10">
@@ -407,10 +440,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,13 +452,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,568 +823,610 @@
   <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="5" width="22.6640625" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="16" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="14"/>
+    <col min="2" max="5" width="22.6640625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" style="14" customWidth="1"/>
+    <col min="7" max="16" width="22.6640625" style="14" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="12">
+        <v>28491</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="C3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="I3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="18">
+        <v>46058</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N5" s="17"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="8">
-        <v>28491</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="B6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="11">
+        <v>33829</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="6">
-        <v>46058</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="F8" s="11">
+        <v>46182</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+    </row>
+    <row r="20" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+    </row>
+    <row r="21" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1343,86 +1444,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>20</v>
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>24</v>
+        <v>58</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
@@ -1510,9 +1617,15 @@
       <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372AF762-1E6D-6C47-A866-2CC8E3395F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E011CDB8-5E0B-514E-88F2-F38E6F98AAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>NOM</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>PRODUCTION DOCUMENT</t>
+  </si>
+  <si>
+    <t>issa.fatoh</t>
   </si>
 </sst>
 </file>
@@ -1135,8 +1138,8 @@
       <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>65</v>
+      <c r="A8" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>65</v>
@@ -1522,7 +1525,7 @@
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>66</v>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E011CDB8-5E0B-514E-88F2-F38E6F98AAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E59EFDE-13D8-6940-893F-3FF487AA03C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="76">
   <si>
     <t>NOM</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>issa.fatoh</t>
+  </si>
+  <si>
+    <t>EN COURS</t>
   </si>
 </sst>
 </file>
@@ -921,7 +924,9 @@
       <c r="M2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="N2" s="9"/>
+      <c r="N2" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
     </row>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E59EFDE-13D8-6940-893F-3FF487AA03C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589F384D-6DF5-7740-AF17-2DFFE9A3388B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
@@ -1114,7 +1114,9 @@
       <c r="C7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="11">
+        <v>37514</v>
+      </c>
       <c r="E7" s="10" t="s">
         <v>27</v>
       </c>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589F384D-6DF5-7740-AF17-2DFFE9A3388B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973427A1-240E-C149-9A1A-00F683AC620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="1" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>user05</t>
   </si>
   <si>
-    <t>user06</t>
-  </si>
-  <si>
     <t>user08</t>
   </si>
   <si>
@@ -221,9 +218,6 @@
     <t>PASSO5</t>
   </si>
   <si>
-    <t>PASS06</t>
-  </si>
-  <si>
     <t>OUI</t>
   </si>
   <si>
@@ -267,6 +261,12 @@
   </si>
   <si>
     <t>EN COURS</t>
+  </si>
+  <si>
+    <t>diabasana</t>
+  </si>
+  <si>
+    <t>HELLOIME2002</t>
   </si>
 </sst>
 </file>
@@ -838,7 +838,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -862,16 +862,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
@@ -891,10 +891,10 @@
         <v>30</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="D2" s="12">
         <v>28491</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>10</v>
@@ -922,10 +922,10 @@
         <v>11</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -935,7 +935,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
@@ -946,7 +946,7 @@
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>10</v>
@@ -964,7 +964,7 @@
         <v>11</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>11</v>
@@ -994,7 +994,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>17</v>
@@ -1012,7 +1012,7 @@
         <v>11</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N4" s="17" t="s">
         <v>11</v>
@@ -1038,7 +1038,7 @@
         <v>22</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>17</v>
@@ -1056,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="10"/>
@@ -1080,7 +1080,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>17</v>
@@ -1098,7 +1098,7 @@
         <v>11</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="10"/>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>25</v>
@@ -1124,7 +1124,7 @@
         <v>28</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>29</v>
@@ -1146,13 +1146,13 @@
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="D8" s="11">
         <v>33829</v>
@@ -1164,7 +1164,7 @@
         <v>46182</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>10</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="9" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="10" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="11" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -1240,7 +1240,7 @@
     </row>
     <row r="12" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="13" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="14" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="15" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="16" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="17" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1380,7 +1380,7 @@
     </row>
     <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="20" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="21" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1455,10 +1455,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>49</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>50</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>0</v>
@@ -1469,10 +1469,10 @@
         <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1480,10 +1480,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1491,7 +1491,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>16</v>
@@ -1502,7 +1502,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>20</v>
@@ -1513,7 +1513,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>20</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>25</v>
@@ -1532,13 +1532,13 @@
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1628,13 +1628,13 @@
     </row>
     <row r="26" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973427A1-240E-C149-9A1A-00F683AC620C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA73EC45-5609-A442-90BD-594FE1EA2D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="1" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
   <si>
     <t>NOM</t>
   </si>
@@ -239,9 +239,6 @@
     <t>FATOH</t>
   </si>
   <si>
-    <t>NON</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -267,6 +264,18 @@
   </si>
   <si>
     <t>HELLOIME2002</t>
+  </si>
+  <si>
+    <t>4 MOIS</t>
+  </si>
+  <si>
+    <t>VALIDE</t>
+  </si>
+  <si>
+    <t>NOVEMBRE</t>
+  </si>
+  <si>
+    <t>DECEMBRE</t>
   </si>
 </sst>
 </file>
@@ -295,7 +304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -305,6 +314,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -490,6 +535,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -862,16 +928,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
@@ -899,14 +965,16 @@
       <c r="D2" s="12">
         <v>28491</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="G2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="16" t="s">
@@ -925,7 +993,7 @@
         <v>59</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -941,18 +1009,20 @@
         <v>13</v>
       </c>
       <c r="D3" s="10"/>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="10" t="s">
+        <v>78</v>
+      </c>
       <c r="G3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J3" s="17" t="s">
         <v>11</v>
@@ -964,13 +1034,13 @@
         <v>11</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="P3" s="18">
         <v>46058</v>
@@ -987,7 +1057,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="10" t="s">
@@ -996,11 +1066,11 @@
       <c r="G4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J4" s="17" t="s">
         <v>11</v>
@@ -1031,7 +1101,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="10"/>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -1040,11 +1110,11 @@
       <c r="G5" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J5" s="17" t="s">
         <v>11</v>
@@ -1073,7 +1143,7 @@
         <v>23</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="24" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="10" t="s">
@@ -1082,11 +1152,11 @@
       <c r="G6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>11</v>
@@ -1106,7 +1176,7 @@
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>25</v>
@@ -1117,7 +1187,7 @@
       <c r="D7" s="11">
         <v>37514</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="25" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -1126,27 +1196,31 @@
       <c r="G7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>59</v>
+      </c>
       <c r="L7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
       <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>63</v>
@@ -1157,20 +1231,24 @@
       <c r="D8" s="11">
         <v>33829</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="23" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="11">
-        <v>46182</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
+        <v>46190</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>72</v>
+      </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
@@ -1521,10 +1599,10 @@
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>25</v>
@@ -1532,7 +1610,7 @@
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>64</v>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA73EC45-5609-A442-90BD-594FE1EA2D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F6C64-06A2-3744-9B8C-D02A279FD02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="80">
   <si>
     <t>NOM</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>DECEMBRE</t>
+  </si>
+  <si>
+    <t>COMPLET</t>
   </si>
 </sst>
 </file>
@@ -972,25 +975,25 @@
         <v>77</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="M2" s="15" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>72</v>
@@ -1016,7 +1019,7 @@
         <v>78</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>10</v>
@@ -1025,10 +1028,10 @@
         <v>59</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="L3" s="17" t="s">
         <v>11</v>
@@ -1064,7 +1067,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>17</v>
@@ -1073,19 +1076,19 @@
         <v>59</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="L4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>11</v>
+        <v>76</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>72</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -1108,7 +1111,7 @@
         <v>22</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>17</v>
@@ -1117,16 +1120,16 @@
         <v>59</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="10"/>
@@ -1150,7 +1153,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>17</v>
@@ -1159,16 +1162,16 @@
         <v>59</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="L6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="10"/>
@@ -1194,7 +1197,7 @@
         <v>28</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>29</v>
@@ -1238,7 +1241,7 @@
         <v>46190</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>75</v>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99F6C64-06A2-3744-9B8C-D02A279FD02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84637A75-0A74-7C43-BF73-1802ABB9E612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="1" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>1MOIS</t>
   </si>
   <si>
-    <t>user01</t>
-  </si>
-  <si>
     <t>user02</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>BELIALBA</t>
   </si>
   <si>
-    <t>PASS01</t>
-  </si>
-  <si>
     <t>PASS02</t>
   </si>
   <si>
@@ -279,6 +273,12 @@
   </si>
   <si>
     <t>COMPLET</t>
+  </si>
+  <si>
+    <t>TINO</t>
+  </si>
+  <si>
+    <t>DELGADO25</t>
   </si>
 </sst>
 </file>
@@ -907,7 +907,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -931,16 +931,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
@@ -957,13 +957,13 @@
     </row>
     <row r="2" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="D2" s="12">
         <v>28491</v>
@@ -972,41 +972,41 @@
         <v>9</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>79</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
@@ -1016,34 +1016,34 @@
         <v>14</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P3" s="18">
         <v>46058</v>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="4" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>16</v>
@@ -1067,35 +1067,35 @@
         <v>19</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>20</v>
@@ -1111,25 +1111,25 @@
         <v>22</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="10"/>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="6" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>20</v>
@@ -1153,25 +1153,25 @@
         <v>24</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="10"/>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>25</v>
@@ -1197,25 +1197,25 @@
         <v>28</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
@@ -1223,13 +1223,13 @@
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="D8" s="11">
         <v>33829</v>
@@ -1241,16 +1241,16 @@
         <v>46190</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="9" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="10" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="11" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="12" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="13" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="14" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="15" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="16" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="17" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="18" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="19" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="20" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="21" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1536,10 +1536,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>0</v>
@@ -1547,32 +1547,32 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>16</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>20</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>20</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>25</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1709,13 +1709,13 @@
     </row>
     <row r="26" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/suivi-dosiers.xlsx
+++ b/suivi-dosiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franklin/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84637A75-0A74-7C43-BF73-1802ABB9E612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5094CB99-55D7-6946-8E5E-1AEDA3CBA505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="1" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{4DF0DB0F-11CA-451E-A870-55A4F60CE8AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Donnees" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,6 @@
     <t>MOT_DE_PASS</t>
   </si>
   <si>
-    <t>DELGADO FERREURA</t>
-  </si>
-  <si>
     <t>FLORENTINO</t>
   </si>
   <si>
@@ -279,6 +276,9 @@
   </si>
   <si>
     <t>DELGADO25</t>
+  </si>
+  <si>
+    <t>DELGADO FERREIRA</t>
   </si>
 </sst>
 </file>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -931,16 +931,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>6</v>
@@ -957,13 +957,13 @@
     </row>
     <row r="2" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="D2" s="12">
         <v>28491</v>
@@ -972,31 +972,31 @@
         <v>9</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -1006,7 +1006,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>13</v>
@@ -1016,34 +1016,34 @@
         <v>14</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="H3" s="21" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="O3" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P3" s="18">
         <v>46058</v>
@@ -1067,28 +1067,28 @@
         <v>19</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L4" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
@@ -1111,25 +1111,25 @@
         <v>22</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L5" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N5" s="17"/>
       <c r="O5" s="10"/>
@@ -1153,25 +1153,25 @@
         <v>24</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N6" s="17"/>
       <c r="O6" s="10"/>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="7" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>25</v>
@@ -1197,25 +1197,25 @@
         <v>28</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
@@ -1223,13 +1223,13 @@
     </row>
     <row r="8" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" s="11">
         <v>33829</v>
@@ -1241,16 +1241,16 @@
         <v>46190</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H8" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
@@ -1547,13 +1547,13 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1561,10 +1561,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1572,7 +1572,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>16</v>
@@ -1583,7 +1583,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>20</v>
@@ -1594,7 +1594,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>20</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>25</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1709,13 +1709,13 @@
     </row>
     <row r="26" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.2"/>
